--- a/Docs/Diccionario Base de Datos OULAD.xlsx
+++ b/Docs/Diccionario Base de Datos OULAD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcabral\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcabral\Downloads\OULAD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DF1658-F98C-428E-B409-D163E170390D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF57B105-D38B-44AE-9ACB-70B8FD372F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,19 +307,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -455,20 +453,38 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -480,13 +496,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -495,12 +511,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -514,165 +524,17 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -692,12 +554,118 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,13 +681,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D49566EB-C43C-489A-860D-1BFC850FFDE7}" name="Table1" displayName="Table1" ref="A1:D44" totalsRowShown="0" headerRowDxfId="0" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D49566EB-C43C-489A-860D-1BFC850FFDE7}" name="Table1" displayName="Table1" ref="A1:D44" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:D44" xr:uid="{D49566EB-C43C-489A-860D-1BFC850FFDE7}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{77115DFC-28AA-4082-9A5F-41D7B6CA2A29}" name="Tabla" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B870B873-5EC1-4F6C-B280-270467FFA994}" name="Columna" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{D60D90A7-C606-4A64-8939-02B024FD6BBF}" name="Tipo de Llave / Restricción" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{AE4A44AD-179A-4A89-8D7E-2488355A2BA9}" name="Descripción Técnica del Campo" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{77115DFC-28AA-4082-9A5F-41D7B6CA2A29}" name="Tabla" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{B870B873-5EC1-4F6C-B280-270467FFA994}" name="Columna" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D60D90A7-C606-4A64-8939-02B024FD6BBF}" name="Tipo de Llave / Restricción" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{AE4A44AD-179A-4A89-8D7E-2488355A2BA9}" name="Descripción Técnica del Campo" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -929,13 +897,13 @@
   <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -949,7 +917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -963,7 +931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -977,7 +945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -991,7 +959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1005,7 +973,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1019,7 +987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
@@ -1033,7 +1001,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -1047,7 +1015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -1061,7 +1029,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1075,7 +1043,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
@@ -1089,7 +1057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -1103,7 +1071,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1117,7 +1085,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1131,7 +1099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -1145,7 +1113,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -1159,7 +1127,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1173,7 +1141,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1187,7 +1155,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1201,7 +1169,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1215,7 +1183,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1229,7 +1197,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>50</v>
       </c>
@@ -1243,7 +1211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>50</v>
       </c>
@@ -1257,7 +1225,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>50</v>
       </c>
@@ -1271,7 +1239,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
@@ -1285,7 +1253,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -1299,7 +1267,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
@@ -1313,7 +1281,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>63</v>
       </c>
@@ -1327,7 +1295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>63</v>
       </c>
@@ -1341,7 +1309,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>63</v>
       </c>
@@ -1355,7 +1323,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>63</v>
       </c>
@@ -1369,7 +1337,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>63</v>
       </c>
@@ -1383,7 +1351,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>73</v>
       </c>
@@ -1397,7 +1365,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>73</v>
       </c>
@@ -1411,7 +1379,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>73</v>
       </c>
@@ -1425,7 +1393,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>73</v>
       </c>
@@ -1439,7 +1407,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>73</v>
       </c>
@@ -1453,7 +1421,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
@@ -1467,7 +1435,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>84</v>
       </c>
@@ -1481,7 +1449,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>84</v>
       </c>
@@ -1495,7 +1463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>84</v>
       </c>
@@ -1509,7 +1477,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -1523,7 +1491,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>84</v>
       </c>
@@ -1537,7 +1505,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>84</v>
       </c>
